--- a/data/trans_orig/IP3108-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3108-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67291</t>
+          <t>67065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77607</t>
+          <t>77917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64795</t>
+          <t>65184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74373</t>
+          <t>74332</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134575</t>
+          <t>136148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149777</t>
+          <t>149643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18685</t>
+          <t>19260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>21834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24289</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40455</t>
+          <t>39344</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24533</t>
+          <t>25183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340835</t>
+          <t>340990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358952</t>
+          <t>359247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>402032</t>
+          <t>402956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>420867</t>
+          <t>420313</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>749161</t>
+          <t>749295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>776181</t>
+          <t>774848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141877</t>
+          <t>142309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152171</t>
+          <t>152022</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128050</t>
+          <t>127136</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>137653</t>
+          <t>137629</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>274196</t>
+          <t>273360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>287918</t>
+          <t>287491</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17237</t>
+          <t>16296</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>29597</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17760</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>13909</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29099</t>
+          <t>28990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30062</t>
+          <t>30279</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35322</t>
+          <t>34614</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>56029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18601</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>559438</t>
+          <t>559304</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>582590</t>
+          <t>583117</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>603326</t>
+          <t>604887</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>626428</t>
+          <t>626172</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1172140</t>
+          <t>1170396</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1204899</t>
+          <t>1203469</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68929</t>
+          <t>69158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72600</t>
+          <t>72585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79446</t>
+          <t>79419</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143891</t>
+          <t>144004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157375</t>
+          <t>157715</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31660</t>
+          <t>31875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22451</t>
+          <t>21254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35933</t>
+          <t>34175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361805</t>
+          <t>361852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>380908</t>
+          <t>379867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>403658</t>
+          <t>402918</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>422155</t>
+          <t>421415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>771010</t>
+          <t>771017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>797963</t>
+          <t>798315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,49 +5070,49 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7459</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>4,85%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2637</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6830</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>135051</t>
+          <t>134685</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145400</t>
+          <t>145591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143353</t>
+          <t>143070</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151358</t>
+          <t>151456</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>282025</t>
+          <t>282178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>295369</t>
+          <t>295473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>15394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31153</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25442</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>23809</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>42633</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>574966</t>
+          <t>574626</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>599087</t>
+          <t>598841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>626517</t>
+          <t>626168</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>648216</t>
+          <t>648701</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1208843</t>
+          <t>1209941</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1240936</t>
+          <t>1241411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44556</t>
+          <t>44508</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51548</t>
+          <t>51881</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56738</t>
+          <t>56057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64335</t>
+          <t>64369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104428</t>
+          <t>104436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114792</t>
+          <t>114723</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>16096</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>29832</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25057</t>
+          <t>24314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14378</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51058</t>
+          <t>49954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>383952</t>
+          <t>384052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>404087</t>
+          <t>404592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>404936</t>
+          <t>403733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>424595</t>
+          <t>423662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>797482</t>
+          <t>795315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>823401</t>
+          <t>822600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18090</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133351</t>
+          <t>132870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>144715</t>
+          <t>144479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>145319</t>
+          <t>145739</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>155668</t>
+          <t>155729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>281518</t>
+          <t>282595</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>297105</t>
+          <t>297854</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23939</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>40098</t>
+          <t>39584</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39425</t>
+          <t>39809</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>43572</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>69069</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>571879</t>
+          <t>572041</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>594843</t>
+          <t>595494</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>615182</t>
+          <t>614476</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>638261</t>
+          <t>638464</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1196092</t>
+          <t>1194613</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1228129</t>
+          <t>1227350</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
